--- a/web/Catalogo_Perfumes.xlsx
+++ b/web/Catalogo_Perfumes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rober\Documents\essence_galery_catalogo\web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD35B98-A1C9-435A-A869-F150380D9BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE0781B9-6F89-44FD-9EAC-A6469721FC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2246,11 +2246,11 @@
         <v>700</v>
       </c>
       <c r="F2" s="5">
-        <f t="shared" ref="F2:F33" si="0">E2+100</f>
-        <v>800</v>
+        <f>E2+200</f>
+        <v>900</v>
       </c>
       <c r="G2" s="5">
-        <v>840</v>
+        <v>1490</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>14</v>
@@ -2279,12 +2279,12 @@
       <c r="E3" s="11">
         <v>650</v>
       </c>
-      <c r="F3" s="11">
-        <f t="shared" si="0"/>
-        <v>750</v>
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F66" si="0">E3+200</f>
+        <v>850</v>
       </c>
       <c r="G3" s="11">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="H3" s="12" t="s">
         <v>14</v>
@@ -2315,10 +2315,10 @@
       </c>
       <c r="F4" s="5">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>1050</v>
       </c>
       <c r="G4" s="5">
-        <v>990</v>
+        <v>1090</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>14</v>
@@ -2347,9 +2347,9 @@
       <c r="E5" s="11">
         <v>990</v>
       </c>
-      <c r="F5" s="11">
-        <f t="shared" si="0"/>
-        <v>1090</v>
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>1190</v>
       </c>
       <c r="G5" s="11">
         <v>1300</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="F6" s="5">
         <f t="shared" si="0"/>
-        <v>790</v>
+        <v>890</v>
       </c>
       <c r="G6" s="5">
         <v>1000</v>
@@ -2411,9 +2411,9 @@
       <c r="E7" s="11">
         <v>790</v>
       </c>
-      <c r="F7" s="11">
-        <f t="shared" si="0"/>
-        <v>890</v>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>990</v>
       </c>
       <c r="G7" s="11">
         <v>1300</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F8" s="5">
         <f t="shared" si="0"/>
-        <v>1490</v>
+        <v>1590</v>
       </c>
       <c r="G8" s="5">
         <v>1900</v>
@@ -2479,12 +2479,12 @@
       <c r="E9" s="11">
         <v>1390</v>
       </c>
-      <c r="F9" s="11">
-        <f t="shared" si="0"/>
-        <v>1490</v>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>1590</v>
       </c>
       <c r="G9" s="11">
-        <v>1590</v>
+        <v>1790</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>14</v>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="F10" s="5">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1090</v>
       </c>
       <c r="G10" s="5">
         <v>1200</v>
@@ -2545,9 +2545,9 @@
       <c r="E11" s="11">
         <v>890</v>
       </c>
-      <c r="F11" s="11">
-        <f t="shared" si="0"/>
-        <v>990</v>
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G11" s="11">
         <v>1400</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="F12" s="5">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1090</v>
       </c>
       <c r="G12" s="5">
         <v>1400</v>
@@ -2611,12 +2611,12 @@
       <c r="E13" s="11">
         <v>900</v>
       </c>
-      <c r="F13" s="11">
-        <f t="shared" si="0"/>
-        <v>1000</v>
+      <c r="F13" s="5">
+        <f t="shared" si="0"/>
+        <v>1100</v>
       </c>
       <c r="G13" s="11">
-        <v>1086</v>
+        <v>1390</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>14</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="F14" s="5">
         <f t="shared" si="0"/>
-        <v>790</v>
+        <v>890</v>
       </c>
       <c r="G14" s="5">
         <v>2088</v>
@@ -2679,9 +2679,9 @@
       <c r="E15" s="11">
         <v>930</v>
       </c>
-      <c r="F15" s="11">
-        <f t="shared" si="0"/>
-        <v>1030</v>
+      <c r="F15" s="5">
+        <f t="shared" si="0"/>
+        <v>1130</v>
       </c>
       <c r="G15" s="11">
         <v>1508</v>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="F16" s="5">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1090</v>
       </c>
       <c r="G16" s="5">
         <v>1508</v>
@@ -2747,9 +2747,9 @@
       <c r="E17" s="11">
         <v>990</v>
       </c>
-      <c r="F17" s="11">
-        <f t="shared" si="0"/>
-        <v>1090</v>
+      <c r="F17" s="5">
+        <f t="shared" si="0"/>
+        <v>1190</v>
       </c>
       <c r="G17" s="11">
         <v>1508</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F18" s="5">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1190</v>
       </c>
       <c r="G18" s="5">
         <v>1508</v>
@@ -2813,9 +2813,9 @@
       <c r="E19" s="11">
         <v>890</v>
       </c>
-      <c r="F19" s="11">
-        <f t="shared" si="0"/>
-        <v>990</v>
+      <c r="F19" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G19" s="11">
         <v>1290</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F20" s="5">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1090</v>
       </c>
       <c r="G20" s="5">
         <v>1390</v>
@@ -2879,9 +2879,9 @@
       <c r="E21" s="11">
         <v>890</v>
       </c>
-      <c r="F21" s="11">
-        <f t="shared" si="0"/>
-        <v>990</v>
+      <c r="F21" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G21" s="11">
         <v>1430</v>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="F22" s="5">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1090</v>
       </c>
       <c r="G22" s="5">
         <v>1500</v>
@@ -2949,9 +2949,9 @@
       <c r="E23" s="11">
         <v>890</v>
       </c>
-      <c r="F23" s="11">
-        <f t="shared" si="0"/>
-        <v>990</v>
+      <c r="F23" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G23" s="11">
         <v>1500</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="F24" s="5">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1190</v>
       </c>
       <c r="G24" s="5">
         <v>1500</v>
@@ -3017,9 +3017,9 @@
       <c r="E25" s="11">
         <v>890</v>
       </c>
-      <c r="F25" s="11">
-        <f t="shared" si="0"/>
-        <v>990</v>
+      <c r="F25" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G25" s="11">
         <v>1500</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="F26" s="5">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1090</v>
       </c>
       <c r="G26" s="5">
         <v>1508</v>
@@ -3085,9 +3085,9 @@
       <c r="E27" s="11">
         <v>890</v>
       </c>
-      <c r="F27" s="11">
-        <f t="shared" si="0"/>
-        <v>990</v>
+      <c r="F27" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G27" s="11">
         <v>1500</v>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="F28" s="5">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1090</v>
       </c>
       <c r="G28" s="5">
         <v>1500</v>
@@ -3153,9 +3153,9 @@
       <c r="E29" s="11">
         <v>890</v>
       </c>
-      <c r="F29" s="11">
-        <f t="shared" si="0"/>
-        <v>990</v>
+      <c r="F29" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G29" s="11">
         <v>1400</v>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="F30" s="5">
         <f t="shared" si="0"/>
-        <v>790</v>
+        <v>890</v>
       </c>
       <c r="G30" s="5">
         <v>1098</v>
@@ -3217,9 +3217,9 @@
       <c r="E31" s="11">
         <v>930</v>
       </c>
-      <c r="F31" s="11">
-        <f t="shared" si="0"/>
-        <v>1030</v>
+      <c r="F31" s="5">
+        <f t="shared" si="0"/>
+        <v>1130</v>
       </c>
       <c r="G31" s="11">
         <v>1430</v>
@@ -3251,10 +3251,10 @@
       </c>
       <c r="F32" s="5">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1090</v>
       </c>
       <c r="G32" s="5">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>14</v>
@@ -3283,9 +3283,9 @@
       <c r="E33" s="11">
         <v>1690</v>
       </c>
-      <c r="F33" s="11">
-        <f t="shared" si="0"/>
-        <v>1790</v>
+      <c r="F33" s="5">
+        <f t="shared" si="0"/>
+        <v>1890</v>
       </c>
       <c r="G33" s="11">
         <v>2930</v>
@@ -3318,8 +3318,8 @@
         <v>2590</v>
       </c>
       <c r="F34" s="5">
-        <f t="shared" ref="F34:F64" si="1">E34+100</f>
-        <v>2690</v>
+        <f t="shared" si="0"/>
+        <v>2790</v>
       </c>
       <c r="G34" s="5">
         <v>3300</v>
@@ -3351,9 +3351,9 @@
       <c r="E35" s="11">
         <v>2590</v>
       </c>
-      <c r="F35" s="11">
-        <f t="shared" si="1"/>
-        <v>2690</v>
+      <c r="F35" s="5">
+        <f t="shared" si="0"/>
+        <v>2790</v>
       </c>
       <c r="G35" s="11">
         <v>3750</v>
@@ -3386,8 +3386,8 @@
         <v>2650</v>
       </c>
       <c r="F36" s="5">
-        <f t="shared" si="1"/>
-        <v>2750</v>
+        <f t="shared" si="0"/>
+        <v>2850</v>
       </c>
       <c r="G36" s="5">
         <v>3300</v>
@@ -3419,9 +3419,9 @@
       <c r="E37" s="11">
         <v>2790</v>
       </c>
-      <c r="F37" s="11">
-        <f t="shared" si="1"/>
-        <v>2890</v>
+      <c r="F37" s="5">
+        <f t="shared" si="0"/>
+        <v>2990</v>
       </c>
       <c r="G37" s="11">
         <v>3990</v>
@@ -3454,8 +3454,8 @@
         <v>1790</v>
       </c>
       <c r="F38" s="5">
-        <f t="shared" si="1"/>
-        <v>1890</v>
+        <f t="shared" si="0"/>
+        <v>1990</v>
       </c>
       <c r="G38" s="5">
         <v>3350</v>
@@ -3487,9 +3487,9 @@
       <c r="E39" s="11">
         <v>2290</v>
       </c>
-      <c r="F39" s="11">
-        <f t="shared" si="1"/>
-        <v>2390</v>
+      <c r="F39" s="5">
+        <f t="shared" si="0"/>
+        <v>2490</v>
       </c>
       <c r="G39" s="11">
         <v>2990</v>
@@ -3522,8 +3522,8 @@
         <v>2290</v>
       </c>
       <c r="F40" s="5">
-        <f t="shared" si="1"/>
-        <v>2390</v>
+        <f t="shared" si="0"/>
+        <v>2490</v>
       </c>
       <c r="G40" s="5">
         <v>2990</v>
@@ -3555,9 +3555,9 @@
       <c r="E41" s="11">
         <v>2590</v>
       </c>
-      <c r="F41" s="11">
-        <f t="shared" si="1"/>
-        <v>2690</v>
+      <c r="F41" s="5">
+        <f t="shared" si="0"/>
+        <v>2790</v>
       </c>
       <c r="G41" s="11">
         <v>3090</v>
@@ -3590,8 +3590,8 @@
         <v>1590</v>
       </c>
       <c r="F42" s="5">
-        <f t="shared" si="1"/>
-        <v>1690</v>
+        <f t="shared" si="0"/>
+        <v>1790</v>
       </c>
       <c r="G42" s="5">
         <v>2950</v>
@@ -3623,9 +3623,9 @@
       <c r="E43" s="11">
         <v>1390</v>
       </c>
-      <c r="F43" s="11">
-        <f t="shared" si="1"/>
-        <v>1490</v>
+      <c r="F43" s="5">
+        <f t="shared" si="0"/>
+        <v>1590</v>
       </c>
       <c r="G43" s="11">
         <v>2790</v>
@@ -3658,8 +3658,8 @@
         <v>2090</v>
       </c>
       <c r="F44" s="5">
-        <f t="shared" si="1"/>
-        <v>2190</v>
+        <f t="shared" si="0"/>
+        <v>2290</v>
       </c>
       <c r="G44" s="5">
         <v>3050</v>
@@ -3691,9 +3691,9 @@
       <c r="E45" s="11">
         <v>1290</v>
       </c>
-      <c r="F45" s="11">
-        <f t="shared" si="1"/>
-        <v>1390</v>
+      <c r="F45" s="5">
+        <f t="shared" si="0"/>
+        <v>1490</v>
       </c>
       <c r="G45" s="11">
         <v>2950</v>
@@ -3723,9 +3723,9 @@
       <c r="E46" s="11">
         <v>1950</v>
       </c>
-      <c r="F46" s="11">
-        <f t="shared" si="1"/>
-        <v>2050</v>
+      <c r="F46" s="5">
+        <f t="shared" si="0"/>
+        <v>2150</v>
       </c>
       <c r="G46" s="11">
         <v>3390</v>
@@ -3758,8 +3758,8 @@
         <v>1190</v>
       </c>
       <c r="F47" s="5">
-        <f t="shared" si="1"/>
-        <v>1290</v>
+        <f t="shared" si="0"/>
+        <v>1390</v>
       </c>
       <c r="G47" s="5">
         <v>1419</v>
@@ -3791,9 +3791,9 @@
       <c r="E48" s="11">
         <v>1690</v>
       </c>
-      <c r="F48" s="11">
-        <f t="shared" si="1"/>
-        <v>1790</v>
+      <c r="F48" s="5">
+        <f t="shared" si="0"/>
+        <v>1890</v>
       </c>
       <c r="G48" s="11">
         <v>2680</v>
@@ -3826,8 +3826,8 @@
         <v>1570</v>
       </c>
       <c r="F49" s="5">
-        <f t="shared" si="1"/>
-        <v>1670</v>
+        <f t="shared" si="0"/>
+        <v>1770</v>
       </c>
       <c r="G49" s="5">
         <v>2550</v>
@@ -3859,9 +3859,9 @@
       <c r="E50" s="11">
         <v>1790</v>
       </c>
-      <c r="F50" s="11">
-        <f t="shared" si="1"/>
-        <v>1890</v>
+      <c r="F50" s="5">
+        <f t="shared" si="0"/>
+        <v>1990</v>
       </c>
       <c r="G50" s="11">
         <v>2680</v>
@@ -3894,8 +3894,8 @@
         <v>2190</v>
       </c>
       <c r="F51" s="5">
-        <f t="shared" si="1"/>
-        <v>2290</v>
+        <f t="shared" si="0"/>
+        <v>2390</v>
       </c>
       <c r="G51" s="5">
         <v>3320</v>
@@ -3927,9 +3927,9 @@
       <c r="E52" s="11">
         <v>1650</v>
       </c>
-      <c r="F52" s="11">
-        <f t="shared" si="1"/>
-        <v>1750</v>
+      <c r="F52" s="5">
+        <f t="shared" si="0"/>
+        <v>1850</v>
       </c>
       <c r="G52" s="11">
         <v>2550</v>
@@ -3962,8 +3962,8 @@
         <v>1890</v>
       </c>
       <c r="F53" s="5">
-        <f t="shared" si="1"/>
-        <v>1990</v>
+        <f t="shared" si="0"/>
+        <v>2090</v>
       </c>
       <c r="G53" s="5">
         <v>2880</v>
@@ -3995,9 +3995,9 @@
       <c r="E54" s="11">
         <v>1890</v>
       </c>
-      <c r="F54" s="11">
-        <f t="shared" si="1"/>
-        <v>1990</v>
+      <c r="F54" s="5">
+        <f t="shared" si="0"/>
+        <v>2090</v>
       </c>
       <c r="G54" s="11">
         <v>3025</v>
@@ -4030,8 +4030,8 @@
         <v>2090</v>
       </c>
       <c r="F55" s="5">
-        <f t="shared" si="1"/>
-        <v>2190</v>
+        <f t="shared" si="0"/>
+        <v>2290</v>
       </c>
       <c r="G55" s="5">
         <v>3455</v>
@@ -4063,9 +4063,9 @@
       <c r="E56" s="11">
         <v>2090</v>
       </c>
-      <c r="F56" s="11">
-        <f t="shared" si="1"/>
-        <v>2190</v>
+      <c r="F56" s="5">
+        <f t="shared" si="0"/>
+        <v>2290</v>
       </c>
       <c r="G56" s="11">
         <v>3170</v>
@@ -4096,8 +4096,8 @@
         <v>1990</v>
       </c>
       <c r="F57" s="5">
-        <f t="shared" si="1"/>
-        <v>2090</v>
+        <f t="shared" si="0"/>
+        <v>2190</v>
       </c>
       <c r="G57" s="5">
         <v>3170</v>
@@ -4129,9 +4129,9 @@
       <c r="E58" s="11">
         <v>1590</v>
       </c>
-      <c r="F58" s="11">
-        <f t="shared" si="1"/>
-        <v>1690</v>
+      <c r="F58" s="5">
+        <f t="shared" si="0"/>
+        <v>1790</v>
       </c>
       <c r="G58" s="11">
         <v>2710</v>
@@ -4164,8 +4164,8 @@
         <v>1490</v>
       </c>
       <c r="F59" s="5">
-        <f t="shared" si="1"/>
-        <v>1590</v>
+        <f t="shared" si="0"/>
+        <v>1690</v>
       </c>
       <c r="G59" s="5">
         <v>2620</v>
@@ -4197,9 +4197,9 @@
       <c r="E60" s="11">
         <v>2090</v>
       </c>
-      <c r="F60" s="11">
-        <f t="shared" si="1"/>
-        <v>2190</v>
+      <c r="F60" s="5">
+        <f t="shared" si="0"/>
+        <v>2290</v>
       </c>
       <c r="G60" s="11">
         <v>2880</v>
@@ -4230,8 +4230,8 @@
         <v>2190</v>
       </c>
       <c r="F61" s="5">
-        <f t="shared" si="1"/>
-        <v>2290</v>
+        <f t="shared" si="0"/>
+        <v>2390</v>
       </c>
       <c r="G61" s="5">
         <v>2990</v>
@@ -4261,9 +4261,9 @@
       <c r="E62" s="11">
         <v>2490</v>
       </c>
-      <c r="F62" s="11">
-        <f t="shared" si="1"/>
-        <v>2590</v>
+      <c r="F62" s="5">
+        <f t="shared" si="0"/>
+        <v>2690</v>
       </c>
       <c r="G62" s="11">
         <v>3500</v>
@@ -4294,8 +4294,8 @@
         <v>2240</v>
       </c>
       <c r="F63" s="5">
-        <f t="shared" si="1"/>
-        <v>2340</v>
+        <f t="shared" si="0"/>
+        <v>2440</v>
       </c>
       <c r="G63" s="5">
         <v>2990</v>
@@ -4327,9 +4327,9 @@
       <c r="E64" s="11">
         <v>2790</v>
       </c>
-      <c r="F64" s="11">
-        <f t="shared" si="1"/>
-        <v>2890</v>
+      <c r="F64" s="5">
+        <f t="shared" si="0"/>
+        <v>2990</v>
       </c>
       <c r="G64" s="11">
         <v>3500</v>
@@ -4362,8 +4362,8 @@
         <v>2490</v>
       </c>
       <c r="F65" s="5">
-        <f t="shared" ref="F65:F96" si="2">E65+100</f>
-        <v>2590</v>
+        <f t="shared" si="0"/>
+        <v>2690</v>
       </c>
       <c r="G65" s="5">
         <v>2880</v>
@@ -4395,9 +4395,9 @@
       <c r="E66" s="11">
         <v>2990</v>
       </c>
-      <c r="F66" s="11">
-        <f t="shared" si="2"/>
-        <v>3090</v>
+      <c r="F66" s="5">
+        <f t="shared" si="0"/>
+        <v>3190</v>
       </c>
       <c r="G66" s="11">
         <v>4100</v>
@@ -4428,8 +4428,8 @@
         <v>3190</v>
       </c>
       <c r="F67" s="5">
-        <f t="shared" si="2"/>
-        <v>3290</v>
+        <f t="shared" ref="F67:F130" si="1">E67+200</f>
+        <v>3390</v>
       </c>
       <c r="G67" s="5">
         <v>4100</v>
@@ -4461,9 +4461,9 @@
       <c r="E68" s="11">
         <v>1590</v>
       </c>
-      <c r="F68" s="11">
-        <f t="shared" si="2"/>
-        <v>1690</v>
+      <c r="F68" s="5">
+        <f t="shared" si="1"/>
+        <v>1790</v>
       </c>
       <c r="G68" s="11">
         <v>3250</v>
@@ -4496,8 +4496,8 @@
         <v>1490</v>
       </c>
       <c r="F69" s="5">
-        <f t="shared" si="2"/>
-        <v>1590</v>
+        <f t="shared" si="1"/>
+        <v>1690</v>
       </c>
       <c r="G69" s="5">
         <v>2290</v>
@@ -4529,9 +4529,9 @@
       <c r="E70" s="11">
         <v>1560</v>
       </c>
-      <c r="F70" s="11">
-        <f t="shared" si="2"/>
-        <v>1660</v>
+      <c r="F70" s="5">
+        <f t="shared" si="1"/>
+        <v>1760</v>
       </c>
       <c r="G70" s="11">
         <v>2600</v>
@@ -4564,11 +4564,11 @@
         <v>750</v>
       </c>
       <c r="F71" s="5">
-        <f t="shared" si="2"/>
-        <v>850</v>
+        <f t="shared" si="1"/>
+        <v>950</v>
       </c>
       <c r="G71" s="5">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>14</v>
@@ -4595,12 +4595,12 @@
       <c r="E72" s="11">
         <v>690</v>
       </c>
-      <c r="F72" s="11">
-        <f t="shared" si="2"/>
-        <v>790</v>
+      <c r="F72" s="5">
+        <f t="shared" si="1"/>
+        <v>890</v>
       </c>
       <c r="G72" s="11">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="H72" s="12" t="s">
         <v>14</v>
@@ -4630,8 +4630,8 @@
         <v>890</v>
       </c>
       <c r="F73" s="5">
-        <f t="shared" si="2"/>
-        <v>990</v>
+        <f t="shared" si="1"/>
+        <v>1090</v>
       </c>
       <c r="G73" s="5">
         <v>1500</v>
@@ -4663,9 +4663,9 @@
       <c r="E74" s="11">
         <v>1090</v>
       </c>
-      <c r="F74" s="11">
-        <f t="shared" si="2"/>
-        <v>1190</v>
+      <c r="F74" s="5">
+        <f t="shared" si="1"/>
+        <v>1290</v>
       </c>
       <c r="G74" s="11">
         <v>1800</v>
@@ -4696,8 +4696,8 @@
         <v>1090</v>
       </c>
       <c r="F75" s="5">
-        <f t="shared" si="2"/>
-        <v>1190</v>
+        <f t="shared" si="1"/>
+        <v>1290</v>
       </c>
       <c r="G75" s="5">
         <v>1700</v>
@@ -4729,9 +4729,9 @@
       <c r="E76" s="11">
         <v>1090</v>
       </c>
-      <c r="F76" s="11">
-        <f t="shared" si="2"/>
-        <v>1190</v>
+      <c r="F76" s="5">
+        <f t="shared" si="1"/>
+        <v>1290</v>
       </c>
       <c r="G76" s="11">
         <v>1500</v>
@@ -4764,8 +4764,8 @@
         <v>1790</v>
       </c>
       <c r="F77" s="5">
-        <f t="shared" si="2"/>
-        <v>1890</v>
+        <f t="shared" si="1"/>
+        <v>1990</v>
       </c>
       <c r="G77" s="5">
         <v>3100</v>
@@ -4795,9 +4795,9 @@
       <c r="E78" s="11">
         <v>1590</v>
       </c>
-      <c r="F78" s="11">
-        <f t="shared" si="2"/>
-        <v>1690</v>
+      <c r="F78" s="5">
+        <f t="shared" si="1"/>
+        <v>1790</v>
       </c>
       <c r="G78" s="11">
         <v>2700</v>
@@ -4828,8 +4828,8 @@
         <v>2290</v>
       </c>
       <c r="F79" s="5">
-        <f t="shared" si="2"/>
-        <v>2390</v>
+        <f t="shared" si="1"/>
+        <v>2490</v>
       </c>
       <c r="G79" s="5">
         <v>3100</v>
@@ -4859,9 +4859,9 @@
       <c r="E80" s="11">
         <v>2590</v>
       </c>
-      <c r="F80" s="11">
-        <f t="shared" si="2"/>
-        <v>2690</v>
+      <c r="F80" s="5">
+        <f t="shared" si="1"/>
+        <v>2790</v>
       </c>
       <c r="G80" s="11">
         <v>3300</v>
@@ -4894,8 +4894,8 @@
         <v>890</v>
       </c>
       <c r="F81" s="5">
-        <f t="shared" si="2"/>
-        <v>990</v>
+        <f t="shared" si="1"/>
+        <v>1090</v>
       </c>
       <c r="G81" s="5">
         <v>1650</v>
@@ -4927,9 +4927,9 @@
       <c r="E82" s="11">
         <v>790</v>
       </c>
-      <c r="F82" s="11">
-        <f t="shared" si="2"/>
-        <v>890</v>
+      <c r="F82" s="5">
+        <f t="shared" si="1"/>
+        <v>990</v>
       </c>
       <c r="G82" s="11">
         <v>1650</v>
@@ -4962,8 +4962,8 @@
         <v>890</v>
       </c>
       <c r="F83" s="5">
-        <f t="shared" si="2"/>
-        <v>990</v>
+        <f t="shared" si="1"/>
+        <v>1090</v>
       </c>
       <c r="G83" s="5">
         <v>1870</v>
@@ -4995,9 +4995,9 @@
       <c r="E84" s="11">
         <v>890</v>
       </c>
-      <c r="F84" s="11">
-        <f t="shared" si="2"/>
-        <v>990</v>
+      <c r="F84" s="5">
+        <f t="shared" si="1"/>
+        <v>1090</v>
       </c>
       <c r="G84" s="11">
         <v>1650</v>
@@ -5030,8 +5030,8 @@
         <v>990</v>
       </c>
       <c r="F85" s="5">
-        <f t="shared" si="2"/>
-        <v>1090</v>
+        <f t="shared" si="1"/>
+        <v>1190</v>
       </c>
       <c r="G85" s="5">
         <v>1650</v>
@@ -5061,12 +5061,12 @@
       <c r="E86" s="11">
         <v>990</v>
       </c>
-      <c r="F86" s="11">
-        <f t="shared" si="2"/>
-        <v>1090</v>
+      <c r="F86" s="5">
+        <f t="shared" si="1"/>
+        <v>1190</v>
       </c>
       <c r="G86" s="11">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="H86" s="12" t="s">
         <v>14</v>
@@ -5094,8 +5094,8 @@
         <v>890</v>
       </c>
       <c r="F87" s="5">
-        <f t="shared" si="2"/>
-        <v>990</v>
+        <f t="shared" si="1"/>
+        <v>1090</v>
       </c>
       <c r="G87" s="5">
         <v>1278</v>
@@ -5125,9 +5125,9 @@
       <c r="E88" s="11">
         <v>990</v>
       </c>
-      <c r="F88" s="11">
-        <f t="shared" si="2"/>
-        <v>1090</v>
+      <c r="F88" s="5">
+        <f t="shared" si="1"/>
+        <v>1190</v>
       </c>
       <c r="G88" s="11">
         <v>1600</v>
@@ -5160,8 +5160,8 @@
         <v>1890</v>
       </c>
       <c r="F89" s="5">
-        <f t="shared" si="2"/>
-        <v>1990</v>
+        <f t="shared" si="1"/>
+        <v>2090</v>
       </c>
       <c r="G89" s="5">
         <v>1940</v>
@@ -5193,9 +5193,9 @@
       <c r="E90" s="11">
         <v>2650</v>
       </c>
-      <c r="F90" s="11">
-        <f t="shared" si="2"/>
-        <v>2750</v>
+      <c r="F90" s="5">
+        <f t="shared" si="1"/>
+        <v>2850</v>
       </c>
       <c r="G90" s="11">
         <v>3380</v>
@@ -5228,8 +5228,8 @@
         <v>2390</v>
       </c>
       <c r="F91" s="5">
-        <f t="shared" si="2"/>
-        <v>2490</v>
+        <f t="shared" si="1"/>
+        <v>2590</v>
       </c>
       <c r="G91" s="5">
         <v>3295</v>
@@ -5261,9 +5261,9 @@
       <c r="E92" s="11">
         <v>2490</v>
       </c>
-      <c r="F92" s="11">
-        <f t="shared" si="2"/>
-        <v>2590</v>
+      <c r="F92" s="5">
+        <f t="shared" si="1"/>
+        <v>2690</v>
       </c>
       <c r="G92" s="11">
         <v>3420</v>
@@ -5296,8 +5296,8 @@
         <v>2490</v>
       </c>
       <c r="F93" s="5">
-        <f t="shared" si="2"/>
-        <v>2590</v>
+        <f t="shared" si="1"/>
+        <v>2690</v>
       </c>
       <c r="G93" s="5">
         <v>3835</v>
@@ -5329,9 +5329,9 @@
       <c r="E94" s="11">
         <v>2390</v>
       </c>
-      <c r="F94" s="11">
-        <f t="shared" si="2"/>
-        <v>2490</v>
+      <c r="F94" s="5">
+        <f t="shared" si="1"/>
+        <v>2590</v>
       </c>
       <c r="G94" s="11">
         <v>3190</v>
@@ -5364,8 +5364,8 @@
         <v>1890</v>
       </c>
       <c r="F95" s="5">
-        <f t="shared" si="2"/>
-        <v>1990</v>
+        <f t="shared" si="1"/>
+        <v>2090</v>
       </c>
       <c r="G95" s="5">
         <v>3535</v>
@@ -5397,9 +5397,9 @@
       <c r="E96" s="11">
         <v>2390</v>
       </c>
-      <c r="F96" s="11">
-        <f t="shared" si="2"/>
-        <v>2490</v>
+      <c r="F96" s="5">
+        <f t="shared" si="1"/>
+        <v>2590</v>
       </c>
       <c r="G96" s="11">
         <v>3625</v>
@@ -5432,8 +5432,8 @@
         <v>2090</v>
       </c>
       <c r="F97" s="5">
-        <f t="shared" ref="F97:F128" si="3">E97+100</f>
-        <v>2190</v>
+        <f t="shared" si="1"/>
+        <v>2290</v>
       </c>
       <c r="G97" s="5">
         <v>3320</v>
@@ -5463,9 +5463,9 @@
       <c r="E98" s="11">
         <v>1890</v>
       </c>
-      <c r="F98" s="11">
-        <f t="shared" si="3"/>
-        <v>1990</v>
+      <c r="F98" s="5">
+        <f t="shared" si="1"/>
+        <v>2090</v>
       </c>
       <c r="G98" s="11">
         <v>2995</v>
@@ -5496,8 +5496,8 @@
         <v>1690</v>
       </c>
       <c r="F99" s="5">
-        <f t="shared" si="3"/>
-        <v>1790</v>
+        <f t="shared" si="1"/>
+        <v>1890</v>
       </c>
       <c r="G99" s="5">
         <v>3000</v>
@@ -5529,9 +5529,9 @@
       <c r="E100" s="11">
         <v>1690</v>
       </c>
-      <c r="F100" s="11">
-        <f t="shared" si="3"/>
-        <v>1790</v>
+      <c r="F100" s="5">
+        <f t="shared" si="1"/>
+        <v>1890</v>
       </c>
       <c r="G100" s="11">
         <v>2700</v>
@@ -5564,8 +5564,8 @@
         <v>1690</v>
       </c>
       <c r="F101" s="5">
-        <f t="shared" si="3"/>
-        <v>1790</v>
+        <f t="shared" si="1"/>
+        <v>1890</v>
       </c>
       <c r="G101" s="5">
         <v>2500</v>
@@ -5597,9 +5597,9 @@
       <c r="E102" s="11">
         <v>1250</v>
       </c>
-      <c r="F102" s="11">
-        <f t="shared" si="3"/>
-        <v>1350</v>
+      <c r="F102" s="5">
+        <f t="shared" si="1"/>
+        <v>1450</v>
       </c>
       <c r="G102" s="11">
         <v>2590</v>
@@ -5632,8 +5632,8 @@
         <v>1190</v>
       </c>
       <c r="F103" s="5">
-        <f t="shared" si="3"/>
-        <v>1290</v>
+        <f t="shared" si="1"/>
+        <v>1390</v>
       </c>
       <c r="G103" s="5">
         <v>1600</v>
@@ -5665,12 +5665,12 @@
       <c r="E104" s="11">
         <v>590</v>
       </c>
-      <c r="F104" s="11">
-        <f t="shared" si="3"/>
-        <v>690</v>
+      <c r="F104" s="5">
+        <f t="shared" si="1"/>
+        <v>790</v>
       </c>
       <c r="G104" s="11">
-        <v>900</v>
+        <v>1400</v>
       </c>
       <c r="H104" s="12" t="s">
         <v>14</v>
@@ -5700,11 +5700,11 @@
         <v>890</v>
       </c>
       <c r="F105" s="5">
-        <f t="shared" si="3"/>
-        <v>990</v>
+        <f t="shared" si="1"/>
+        <v>1090</v>
       </c>
       <c r="G105" s="5">
-        <v>1100</v>
+        <v>1490</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>14</v>
@@ -5733,12 +5733,12 @@
       <c r="E106" s="11">
         <v>690</v>
       </c>
-      <c r="F106" s="11">
-        <f t="shared" si="3"/>
-        <v>790</v>
+      <c r="F106" s="5">
+        <f t="shared" si="1"/>
+        <v>890</v>
       </c>
       <c r="G106" s="11">
-        <v>890</v>
+        <v>1400</v>
       </c>
       <c r="H106" s="12" t="s">
         <v>14</v>
@@ -5766,8 +5766,8 @@
         <v>790</v>
       </c>
       <c r="F107" s="5">
-        <f t="shared" si="3"/>
-        <v>890</v>
+        <f t="shared" si="1"/>
+        <v>990</v>
       </c>
       <c r="G107" s="5">
         <v>1300</v>
@@ -5799,12 +5799,12 @@
       <c r="E108" s="11">
         <v>590</v>
       </c>
-      <c r="F108" s="11">
-        <f t="shared" si="3"/>
-        <v>690</v>
+      <c r="F108" s="5">
+        <f t="shared" si="1"/>
+        <v>790</v>
       </c>
       <c r="G108" s="11">
-        <v>800</v>
+        <v>1390</v>
       </c>
       <c r="H108" s="12" t="s">
         <v>14</v>
@@ -5832,8 +5832,8 @@
         <v>1040</v>
       </c>
       <c r="F109" s="5">
-        <f t="shared" si="3"/>
-        <v>1140</v>
+        <f t="shared" si="1"/>
+        <v>1240</v>
       </c>
       <c r="G109" s="5">
         <v>1557</v>
@@ -5865,9 +5865,9 @@
       <c r="E110" s="11">
         <v>790</v>
       </c>
-      <c r="F110" s="11">
-        <f t="shared" si="3"/>
-        <v>890</v>
+      <c r="F110" s="5">
+        <f t="shared" si="1"/>
+        <v>990</v>
       </c>
       <c r="G110" s="11">
         <v>1350</v>
@@ -5900,11 +5900,11 @@
         <v>690</v>
       </c>
       <c r="F111" s="5">
-        <f t="shared" si="3"/>
-        <v>790</v>
+        <f t="shared" si="1"/>
+        <v>890</v>
       </c>
       <c r="G111" s="5">
-        <v>900</v>
+        <v>1490</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>14</v>
@@ -5933,12 +5933,12 @@
       <c r="E112" s="11">
         <v>690</v>
       </c>
-      <c r="F112" s="11">
-        <f t="shared" si="3"/>
-        <v>790</v>
+      <c r="F112" s="5">
+        <f t="shared" si="1"/>
+        <v>890</v>
       </c>
       <c r="G112" s="11">
-        <v>940</v>
+        <v>1490</v>
       </c>
       <c r="H112" s="12" t="s">
         <v>14</v>
@@ -5968,11 +5968,11 @@
         <v>990</v>
       </c>
       <c r="F113" s="5">
-        <f t="shared" si="3"/>
-        <v>1090</v>
+        <f t="shared" si="1"/>
+        <v>1190</v>
       </c>
       <c r="G113" s="5">
-        <v>1290</v>
+        <v>1500</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>14</v>
@@ -6001,12 +6001,12 @@
       <c r="E114" s="11">
         <v>930</v>
       </c>
-      <c r="F114" s="11">
-        <f t="shared" si="3"/>
-        <v>1030</v>
+      <c r="F114" s="5">
+        <f t="shared" si="1"/>
+        <v>1130</v>
       </c>
       <c r="G114" s="11">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="H114" s="12" t="s">
         <v>14</v>
@@ -6038,8 +6038,8 @@
         <v>790</v>
       </c>
       <c r="F115" s="5">
-        <f t="shared" si="3"/>
-        <v>890</v>
+        <f t="shared" si="1"/>
+        <v>990</v>
       </c>
       <c r="G115" s="5">
         <v>1400</v>
@@ -6069,12 +6069,12 @@
       <c r="E116" s="11">
         <v>599</v>
       </c>
-      <c r="F116" s="11">
-        <f t="shared" si="3"/>
-        <v>699</v>
+      <c r="F116" s="5">
+        <f t="shared" si="1"/>
+        <v>799</v>
       </c>
       <c r="G116" s="11">
-        <v>599</v>
+        <v>1299</v>
       </c>
       <c r="H116" s="12" t="s">
         <v>14</v>
@@ -6104,8 +6104,8 @@
         <v>990</v>
       </c>
       <c r="F117" s="5">
-        <f t="shared" si="3"/>
-        <v>1090</v>
+        <f t="shared" si="1"/>
+        <v>1190</v>
       </c>
       <c r="G117" s="5">
         <v>1500</v>
@@ -6135,9 +6135,9 @@
       <c r="E118" s="11">
         <v>2090</v>
       </c>
-      <c r="F118" s="11">
-        <f t="shared" si="3"/>
-        <v>2190</v>
+      <c r="F118" s="5">
+        <f t="shared" si="1"/>
+        <v>2290</v>
       </c>
       <c r="G118" s="11">
         <v>3450</v>
@@ -6168,8 +6168,8 @@
         <v>2090</v>
       </c>
       <c r="F119" s="5">
-        <f t="shared" si="3"/>
-        <v>2190</v>
+        <f t="shared" si="1"/>
+        <v>2290</v>
       </c>
       <c r="G119" s="5">
         <v>3420</v>
@@ -6201,9 +6201,9 @@
       <c r="E120" s="11">
         <v>1120</v>
       </c>
-      <c r="F120" s="11">
-        <f t="shared" si="3"/>
-        <v>1220</v>
+      <c r="F120" s="5">
+        <f t="shared" si="1"/>
+        <v>1320</v>
       </c>
       <c r="G120" s="11">
         <v>2920</v>
@@ -6236,8 +6236,8 @@
         <v>2250</v>
       </c>
       <c r="F121" s="5">
-        <f t="shared" si="3"/>
-        <v>2350</v>
+        <f t="shared" si="1"/>
+        <v>2450</v>
       </c>
       <c r="G121" s="5">
         <v>3350</v>
@@ -6269,9 +6269,9 @@
       <c r="E122" s="11">
         <v>1190</v>
       </c>
-      <c r="F122" s="11">
-        <f t="shared" si="3"/>
-        <v>1290</v>
+      <c r="F122" s="5">
+        <f t="shared" si="1"/>
+        <v>1390</v>
       </c>
       <c r="G122" s="11">
         <v>2920</v>
@@ -6304,8 +6304,8 @@
         <v>950</v>
       </c>
       <c r="F123" s="5">
-        <f t="shared" si="3"/>
-        <v>1050</v>
+        <f t="shared" si="1"/>
+        <v>1150</v>
       </c>
       <c r="G123" s="5">
         <v>1800</v>
@@ -6335,9 +6335,9 @@
       <c r="E124" s="11">
         <v>1290</v>
       </c>
-      <c r="F124" s="11">
-        <f t="shared" si="3"/>
-        <v>1390</v>
+      <c r="F124" s="5">
+        <f t="shared" si="1"/>
+        <v>1490</v>
       </c>
       <c r="G124" s="11">
         <v>2920</v>
@@ -6370,8 +6370,8 @@
         <v>1150</v>
       </c>
       <c r="F125" s="5">
-        <f t="shared" si="3"/>
-        <v>1250</v>
+        <f t="shared" si="1"/>
+        <v>1350</v>
       </c>
       <c r="G125" s="5">
         <v>2920</v>
@@ -6403,9 +6403,9 @@
       <c r="E126" s="11">
         <v>990</v>
       </c>
-      <c r="F126" s="11">
-        <f t="shared" si="3"/>
-        <v>1090</v>
+      <c r="F126" s="5">
+        <f t="shared" si="1"/>
+        <v>1190</v>
       </c>
       <c r="G126" s="11">
         <v>2750</v>
@@ -6438,8 +6438,8 @@
         <v>390</v>
       </c>
       <c r="F127" s="5">
-        <f t="shared" si="3"/>
-        <v>490</v>
+        <f t="shared" si="1"/>
+        <v>590</v>
       </c>
       <c r="G127" s="5">
         <v>950</v>
@@ -6471,12 +6471,12 @@
       <c r="E128" s="11">
         <v>650</v>
       </c>
-      <c r="F128" s="11">
-        <f t="shared" si="3"/>
-        <v>750</v>
+      <c r="F128" s="5">
+        <f t="shared" si="1"/>
+        <v>850</v>
       </c>
       <c r="G128" s="11">
-        <v>800</v>
+        <v>1390</v>
       </c>
       <c r="H128" s="12" t="s">
         <v>14</v>
@@ -6506,11 +6506,11 @@
         <v>990</v>
       </c>
       <c r="F129" s="5">
-        <f t="shared" ref="F129:F160" si="4">E129+100</f>
-        <v>1090</v>
+        <f t="shared" si="1"/>
+        <v>1190</v>
       </c>
       <c r="G129" s="5">
-        <v>1390</v>
+        <v>1590</v>
       </c>
       <c r="H129" s="6" t="s">
         <v>14</v>
@@ -6539,9 +6539,9 @@
       <c r="E130" s="11">
         <v>1190</v>
       </c>
-      <c r="F130" s="11">
-        <f t="shared" si="4"/>
-        <v>1290</v>
+      <c r="F130" s="5">
+        <f t="shared" si="1"/>
+        <v>1390</v>
       </c>
       <c r="G130" s="11">
         <v>3100</v>
@@ -6576,8 +6576,8 @@
         <v>1090</v>
       </c>
       <c r="F131" s="5">
-        <f t="shared" si="4"/>
-        <v>1190</v>
+        <f t="shared" ref="F131:F184" si="2">E131+200</f>
+        <v>1290</v>
       </c>
       <c r="G131" s="5">
         <v>3100</v>
@@ -6609,9 +6609,9 @@
       <c r="E132" s="11">
         <v>1590</v>
       </c>
-      <c r="F132" s="11">
-        <f t="shared" si="4"/>
-        <v>1690</v>
+      <c r="F132" s="5">
+        <f t="shared" si="2"/>
+        <v>1790</v>
       </c>
       <c r="G132" s="11">
         <v>2790</v>
@@ -6644,8 +6644,8 @@
         <v>1890</v>
       </c>
       <c r="F133" s="5">
-        <f t="shared" si="4"/>
-        <v>1990</v>
+        <f t="shared" si="2"/>
+        <v>2090</v>
       </c>
       <c r="G133" s="5">
         <v>2790</v>
@@ -6677,9 +6677,9 @@
       <c r="E134" s="11">
         <v>2190</v>
       </c>
-      <c r="F134" s="11">
-        <f t="shared" si="4"/>
-        <v>2290</v>
+      <c r="F134" s="5">
+        <f t="shared" si="2"/>
+        <v>2390</v>
       </c>
       <c r="G134" s="11">
         <v>3210</v>
@@ -6712,8 +6712,8 @@
         <v>2190</v>
       </c>
       <c r="F135" s="5">
-        <f t="shared" si="4"/>
-        <v>2290</v>
+        <f t="shared" si="2"/>
+        <v>2390</v>
       </c>
       <c r="G135" s="5">
         <v>3150</v>
@@ -6745,9 +6745,9 @@
       <c r="E136" s="11">
         <v>1990</v>
       </c>
-      <c r="F136" s="11">
-        <f t="shared" si="4"/>
-        <v>2090</v>
+      <c r="F136" s="5">
+        <f t="shared" si="2"/>
+        <v>2190</v>
       </c>
       <c r="G136" s="11">
         <v>3210</v>
@@ -6780,8 +6780,8 @@
         <v>2090</v>
       </c>
       <c r="F137" s="5">
-        <f t="shared" si="4"/>
-        <v>2190</v>
+        <f t="shared" si="2"/>
+        <v>2290</v>
       </c>
       <c r="G137" s="5">
         <v>3350</v>
@@ -6813,9 +6813,9 @@
       <c r="E138" s="11">
         <v>1590</v>
       </c>
-      <c r="F138" s="11">
-        <f t="shared" si="4"/>
-        <v>1690</v>
+      <c r="F138" s="5">
+        <f t="shared" si="2"/>
+        <v>1790</v>
       </c>
       <c r="G138" s="11">
         <v>2040</v>
@@ -6848,8 +6848,8 @@
         <v>2190</v>
       </c>
       <c r="F139" s="5">
-        <f t="shared" si="4"/>
-        <v>2290</v>
+        <f t="shared" si="2"/>
+        <v>2390</v>
       </c>
       <c r="G139" s="5">
         <v>3350</v>
@@ -6881,9 +6881,9 @@
       <c r="E140" s="11">
         <v>1990</v>
       </c>
-      <c r="F140" s="11">
-        <f t="shared" si="4"/>
-        <v>2090</v>
+      <c r="F140" s="5">
+        <f t="shared" si="2"/>
+        <v>2190</v>
       </c>
       <c r="G140" s="11">
         <v>3250</v>
@@ -6916,8 +6916,8 @@
         <v>2090</v>
       </c>
       <c r="F141" s="5">
-        <f t="shared" si="4"/>
-        <v>2190</v>
+        <f t="shared" si="2"/>
+        <v>2290</v>
       </c>
       <c r="G141" s="5">
         <v>3210</v>
@@ -6949,9 +6949,9 @@
       <c r="E142" s="11">
         <v>1890</v>
       </c>
-      <c r="F142" s="11">
-        <f t="shared" si="4"/>
-        <v>1990</v>
+      <c r="F142" s="5">
+        <f t="shared" si="2"/>
+        <v>2090</v>
       </c>
       <c r="G142" s="11">
         <v>2850</v>
@@ -6984,8 +6984,8 @@
         <v>1990</v>
       </c>
       <c r="F143" s="5">
-        <f t="shared" si="4"/>
-        <v>2090</v>
+        <f t="shared" si="2"/>
+        <v>2190</v>
       </c>
       <c r="G143" s="5">
         <v>3080</v>
@@ -7017,9 +7017,9 @@
       <c r="E144" s="11">
         <v>2090</v>
       </c>
-      <c r="F144" s="11">
-        <f t="shared" si="4"/>
-        <v>2190</v>
+      <c r="F144" s="5">
+        <f t="shared" si="2"/>
+        <v>2290</v>
       </c>
       <c r="G144" s="11">
         <v>3200</v>
@@ -7050,11 +7050,11 @@
         <v>6800</v>
       </c>
       <c r="F145" s="5">
-        <f t="shared" si="4"/>
-        <v>6900</v>
+        <f t="shared" si="2"/>
+        <v>7000</v>
       </c>
       <c r="G145" s="5">
-        <v>8200</v>
+        <v>8600</v>
       </c>
       <c r="H145" s="6" t="s">
         <v>14</v>
@@ -7081,9 +7081,9 @@
       <c r="E146" s="11">
         <v>6200</v>
       </c>
-      <c r="F146" s="11">
-        <f t="shared" si="4"/>
-        <v>6300</v>
+      <c r="F146" s="5">
+        <f t="shared" si="2"/>
+        <v>6400</v>
       </c>
       <c r="G146" s="11">
         <v>8200</v>
@@ -7114,8 +7114,8 @@
         <v>1590</v>
       </c>
       <c r="F147" s="5">
-        <f t="shared" si="4"/>
-        <v>1690</v>
+        <f t="shared" si="2"/>
+        <v>1790</v>
       </c>
       <c r="G147" s="5">
         <v>2430</v>
@@ -7147,12 +7147,12 @@
       <c r="E148" s="11">
         <v>790</v>
       </c>
-      <c r="F148" s="11">
-        <f t="shared" si="4"/>
-        <v>890</v>
+      <c r="F148" s="5">
+        <f t="shared" si="2"/>
+        <v>990</v>
       </c>
       <c r="G148" s="11">
-        <v>1000</v>
+        <v>1490</v>
       </c>
       <c r="H148" s="12" t="s">
         <v>14</v>
@@ -7182,8 +7182,8 @@
         <v>1150</v>
       </c>
       <c r="F149" s="5">
-        <f t="shared" si="4"/>
-        <v>1250</v>
+        <f t="shared" si="2"/>
+        <v>1350</v>
       </c>
       <c r="G149" s="5">
         <v>1790</v>
@@ -7215,12 +7215,12 @@
       <c r="E150" s="11">
         <v>1190</v>
       </c>
-      <c r="F150" s="11">
-        <f t="shared" si="4"/>
-        <v>1290</v>
+      <c r="F150" s="5">
+        <f t="shared" si="2"/>
+        <v>1390</v>
       </c>
       <c r="G150" s="11">
-        <v>1500</v>
+        <v>1790</v>
       </c>
       <c r="H150" s="12" t="s">
         <v>14</v>
@@ -7250,11 +7250,11 @@
         <v>1290</v>
       </c>
       <c r="F151" s="5">
-        <f t="shared" si="4"/>
-        <v>1390</v>
+        <f t="shared" si="2"/>
+        <v>1490</v>
       </c>
       <c r="G151" s="5">
-        <v>1750</v>
+        <v>1850</v>
       </c>
       <c r="H151" s="6" t="s">
         <v>14</v>
@@ -7283,9 +7283,9 @@
       <c r="E152" s="11">
         <v>990</v>
       </c>
-      <c r="F152" s="11">
-        <f t="shared" si="4"/>
-        <v>1090</v>
+      <c r="F152" s="5">
+        <f t="shared" si="2"/>
+        <v>1190</v>
       </c>
       <c r="G152" s="11">
         <v>1700</v>
@@ -7318,11 +7318,11 @@
         <v>1090</v>
       </c>
       <c r="F153" s="5">
-        <f t="shared" si="4"/>
-        <v>1190</v>
+        <f t="shared" si="2"/>
+        <v>1290</v>
       </c>
       <c r="G153" s="5">
-        <v>1500</v>
+        <v>1650</v>
       </c>
       <c r="H153" s="6" t="s">
         <v>14</v>
@@ -7351,9 +7351,9 @@
       <c r="E154" s="11">
         <v>1090</v>
       </c>
-      <c r="F154" s="11">
-        <f t="shared" si="4"/>
-        <v>1190</v>
+      <c r="F154" s="5">
+        <f t="shared" si="2"/>
+        <v>1290</v>
       </c>
       <c r="G154" s="11">
         <v>1490</v>
@@ -7386,11 +7386,11 @@
         <v>1190</v>
       </c>
       <c r="F155" s="5">
-        <f t="shared" si="4"/>
-        <v>1290</v>
+        <f t="shared" si="2"/>
+        <v>1390</v>
       </c>
       <c r="G155" s="5">
-        <v>1490</v>
+        <v>1790</v>
       </c>
       <c r="H155" s="6" t="s">
         <v>14</v>
@@ -7419,9 +7419,9 @@
       <c r="E156" s="11">
         <v>1290</v>
       </c>
-      <c r="F156" s="11">
-        <f t="shared" si="4"/>
-        <v>1390</v>
+      <c r="F156" s="5">
+        <f t="shared" si="2"/>
+        <v>1490</v>
       </c>
       <c r="G156" s="11">
         <v>1720</v>
@@ -7452,11 +7452,11 @@
         <v>890</v>
       </c>
       <c r="F157" s="5">
-        <f t="shared" si="4"/>
-        <v>990</v>
+        <f t="shared" si="2"/>
+        <v>1090</v>
       </c>
       <c r="G157" s="5">
-        <v>890</v>
+        <v>1890</v>
       </c>
       <c r="H157" s="6" t="s">
         <v>14</v>
@@ -7485,9 +7485,9 @@
       <c r="E158" s="11">
         <v>2190</v>
       </c>
-      <c r="F158" s="11">
-        <f t="shared" si="4"/>
-        <v>2290</v>
+      <c r="F158" s="5">
+        <f t="shared" si="2"/>
+        <v>2390</v>
       </c>
       <c r="G158" s="11">
         <v>2980</v>
@@ -7520,8 +7520,8 @@
         <v>2190</v>
       </c>
       <c r="F159" s="5">
-        <f t="shared" si="4"/>
-        <v>2290</v>
+        <f t="shared" si="2"/>
+        <v>2390</v>
       </c>
       <c r="G159" s="5">
         <v>2980</v>
@@ -7553,9 +7553,9 @@
       <c r="E160" s="11">
         <v>3190</v>
       </c>
-      <c r="F160" s="11">
-        <f t="shared" si="4"/>
-        <v>3290</v>
+      <c r="F160" s="5">
+        <f t="shared" si="2"/>
+        <v>3390</v>
       </c>
       <c r="G160" s="11">
         <v>4090</v>
@@ -7588,8 +7588,8 @@
         <v>2090</v>
       </c>
       <c r="F161" s="5">
-        <f t="shared" ref="F161:F184" si="5">E161+100</f>
-        <v>2190</v>
+        <f t="shared" si="2"/>
+        <v>2290</v>
       </c>
       <c r="G161" s="5">
         <v>2980</v>
@@ -7621,9 +7621,9 @@
       <c r="E162" s="11">
         <v>2890</v>
       </c>
-      <c r="F162" s="11">
-        <f t="shared" si="5"/>
-        <v>2990</v>
+      <c r="F162" s="5">
+        <f t="shared" si="2"/>
+        <v>3090</v>
       </c>
       <c r="G162" s="11">
         <v>3750</v>
@@ -7654,11 +7654,11 @@
         <v>890</v>
       </c>
       <c r="F163" s="5">
-        <f t="shared" si="5"/>
-        <v>990</v>
+        <f t="shared" si="2"/>
+        <v>1090</v>
       </c>
       <c r="G163" s="5">
-        <v>950</v>
+        <v>1950</v>
       </c>
       <c r="H163" s="6" t="s">
         <v>14</v>
@@ -7687,9 +7687,9 @@
       <c r="E164" s="11">
         <v>1290</v>
       </c>
-      <c r="F164" s="11">
-        <f t="shared" si="5"/>
-        <v>1390</v>
+      <c r="F164" s="5">
+        <f t="shared" si="2"/>
+        <v>1490</v>
       </c>
       <c r="G164" s="11">
         <v>2650</v>
@@ -7722,8 +7722,8 @@
         <v>1490</v>
       </c>
       <c r="F165" s="5">
-        <f t="shared" si="5"/>
-        <v>1590</v>
+        <f t="shared" si="2"/>
+        <v>1690</v>
       </c>
       <c r="G165" s="5">
         <v>3100</v>
@@ -7755,9 +7755,9 @@
       <c r="E166" s="11">
         <v>1350</v>
       </c>
-      <c r="F166" s="11">
-        <f t="shared" si="5"/>
-        <v>1450</v>
+      <c r="F166" s="5">
+        <f t="shared" si="2"/>
+        <v>1550</v>
       </c>
       <c r="G166" s="11">
         <v>2650</v>
@@ -7790,8 +7790,8 @@
         <v>1990</v>
       </c>
       <c r="F167" s="5">
-        <f t="shared" si="5"/>
-        <v>2090</v>
+        <f t="shared" si="2"/>
+        <v>2190</v>
       </c>
       <c r="G167" s="5">
         <v>3100</v>
@@ -7823,9 +7823,9 @@
       <c r="E168" s="11">
         <v>1590</v>
       </c>
-      <c r="F168" s="11">
-        <f t="shared" si="5"/>
-        <v>1690</v>
+      <c r="F168" s="5">
+        <f t="shared" si="2"/>
+        <v>1790</v>
       </c>
       <c r="G168" s="11">
         <v>2970</v>
@@ -7858,8 +7858,8 @@
         <v>1790</v>
       </c>
       <c r="F169" s="5">
-        <f t="shared" si="5"/>
-        <v>1890</v>
+        <f t="shared" si="2"/>
+        <v>1990</v>
       </c>
       <c r="G169" s="5">
         <v>4100</v>
@@ -7891,9 +7891,9 @@
       <c r="E170" s="11">
         <v>1190</v>
       </c>
-      <c r="F170" s="11">
-        <f t="shared" si="5"/>
-        <v>1290</v>
+      <c r="F170" s="5">
+        <f t="shared" si="2"/>
+        <v>1390</v>
       </c>
       <c r="G170" s="11">
         <v>2650</v>
@@ -7926,8 +7926,8 @@
         <v>1190</v>
       </c>
       <c r="F171" s="5">
-        <f t="shared" si="5"/>
-        <v>1290</v>
+        <f t="shared" si="2"/>
+        <v>1390</v>
       </c>
       <c r="G171" s="5">
         <v>2650</v>
@@ -7957,9 +7957,9 @@
       <c r="E172" s="11">
         <v>1890</v>
       </c>
-      <c r="F172" s="11">
-        <f t="shared" si="5"/>
-        <v>1990</v>
+      <c r="F172" s="5">
+        <f t="shared" si="2"/>
+        <v>2090</v>
       </c>
       <c r="G172" s="11">
         <v>3700</v>
@@ -7990,8 +7990,8 @@
         <v>2490</v>
       </c>
       <c r="F173" s="5">
-        <f t="shared" si="5"/>
-        <v>2590</v>
+        <f t="shared" si="2"/>
+        <v>2690</v>
       </c>
       <c r="G173" s="5">
         <v>3950</v>
@@ -8021,9 +8021,9 @@
       <c r="E174" s="11">
         <v>2190</v>
       </c>
-      <c r="F174" s="11">
-        <f t="shared" si="5"/>
-        <v>2290</v>
+      <c r="F174" s="5">
+        <f t="shared" si="2"/>
+        <v>2390</v>
       </c>
       <c r="G174" s="11">
         <v>3050</v>
@@ -8054,8 +8054,8 @@
         <v>2390</v>
       </c>
       <c r="F175" s="5">
-        <f t="shared" si="5"/>
-        <v>2490</v>
+        <f t="shared" si="2"/>
+        <v>2590</v>
       </c>
       <c r="G175" s="5">
         <v>3950</v>
@@ -8085,9 +8085,9 @@
       <c r="E176" s="11">
         <v>1990</v>
       </c>
-      <c r="F176" s="11">
-        <f t="shared" si="5"/>
-        <v>2090</v>
+      <c r="F176" s="5">
+        <f t="shared" si="2"/>
+        <v>2190</v>
       </c>
       <c r="G176" s="11">
         <v>3700</v>
@@ -8118,8 +8118,8 @@
         <v>2190</v>
       </c>
       <c r="F177" s="5">
-        <f t="shared" si="5"/>
-        <v>2290</v>
+        <f t="shared" si="2"/>
+        <v>2390</v>
       </c>
       <c r="G177" s="5">
         <v>3950</v>
@@ -8149,9 +8149,9 @@
       <c r="E178" s="11">
         <v>5300</v>
       </c>
-      <c r="F178" s="11">
-        <f t="shared" si="5"/>
-        <v>5400</v>
+      <c r="F178" s="5">
+        <f t="shared" si="2"/>
+        <v>5500</v>
       </c>
       <c r="G178" s="11">
         <v>6600</v>
@@ -8182,8 +8182,8 @@
         <v>5300</v>
       </c>
       <c r="F179" s="5">
-        <f t="shared" si="5"/>
-        <v>5400</v>
+        <f t="shared" si="2"/>
+        <v>5500</v>
       </c>
       <c r="G179" s="5">
         <v>6600</v>
@@ -8213,9 +8213,9 @@
       <c r="E180" s="11">
         <v>2390</v>
       </c>
-      <c r="F180" s="11">
-        <f t="shared" si="5"/>
-        <v>2490</v>
+      <c r="F180" s="5">
+        <f t="shared" si="2"/>
+        <v>2590</v>
       </c>
       <c r="G180" s="11">
         <v>3600</v>
@@ -8246,8 +8246,8 @@
         <v>2390</v>
       </c>
       <c r="F181" s="5">
-        <f t="shared" si="5"/>
-        <v>2490</v>
+        <f t="shared" si="2"/>
+        <v>2590</v>
       </c>
       <c r="G181" s="5">
         <v>3600</v>
@@ -8277,9 +8277,9 @@
       <c r="E182" s="11">
         <v>2090</v>
       </c>
-      <c r="F182" s="11">
-        <f t="shared" si="5"/>
-        <v>2190</v>
+      <c r="F182" s="5">
+        <f t="shared" si="2"/>
+        <v>2290</v>
       </c>
       <c r="G182" s="11">
         <v>2980</v>
@@ -8310,8 +8310,8 @@
         <v>2390</v>
       </c>
       <c r="F183" s="5">
-        <f t="shared" si="5"/>
-        <v>2490</v>
+        <f t="shared" si="2"/>
+        <v>2590</v>
       </c>
       <c r="G183" s="5">
         <v>3750</v>
@@ -8341,9 +8341,9 @@
       <c r="E184" s="11">
         <v>2390</v>
       </c>
-      <c r="F184" s="11">
-        <f t="shared" si="5"/>
-        <v>2490</v>
+      <c r="F184" s="5">
+        <f t="shared" si="2"/>
+        <v>2590</v>
       </c>
       <c r="G184" s="11">
         <v>4100</v>
@@ -8442,8 +8442,8 @@
         <v>990</v>
       </c>
       <c r="F2" s="5">
-        <f t="shared" ref="F2:F33" si="0">E2+100</f>
-        <v>1090</v>
+        <f>E2+200</f>
+        <v>1190</v>
       </c>
       <c r="G2" s="5">
         <v>1900</v>
@@ -8475,9 +8475,9 @@
       <c r="E3" s="11">
         <v>1390</v>
       </c>
-      <c r="F3" s="11">
-        <f t="shared" si="0"/>
-        <v>1490</v>
+      <c r="F3" s="5">
+        <f t="shared" ref="F3:F66" si="0">E3+200</f>
+        <v>1590</v>
       </c>
       <c r="G3" s="11">
         <v>2100</v>
@@ -8509,7 +8509,7 @@
       </c>
       <c r="F4" s="5">
         <f t="shared" si="0"/>
-        <v>1490</v>
+        <v>1590</v>
       </c>
       <c r="G4" s="5">
         <v>2100</v>
@@ -8541,9 +8541,9 @@
       <c r="E5" s="11">
         <v>1490</v>
       </c>
-      <c r="F5" s="11">
-        <f t="shared" si="0"/>
-        <v>1590</v>
+      <c r="F5" s="5">
+        <f t="shared" si="0"/>
+        <v>1690</v>
       </c>
       <c r="G5" s="11">
         <v>2100</v>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="F6" s="5">
         <f t="shared" si="0"/>
-        <v>1320</v>
+        <v>1420</v>
       </c>
       <c r="G6" s="5">
         <v>1900</v>
@@ -8609,9 +8609,9 @@
       <c r="E7" s="11">
         <v>1240</v>
       </c>
-      <c r="F7" s="11">
-        <f t="shared" si="0"/>
-        <v>1340</v>
+      <c r="F7" s="5">
+        <f t="shared" si="0"/>
+        <v>1440</v>
       </c>
       <c r="G7" s="11">
         <v>2000</v>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="F8" s="5">
         <f t="shared" si="0"/>
-        <v>1290</v>
+        <v>1390</v>
       </c>
       <c r="G8" s="5">
         <v>2000</v>
@@ -8677,9 +8677,9 @@
       <c r="E9" s="11">
         <v>990</v>
       </c>
-      <c r="F9" s="11">
-        <f t="shared" si="0"/>
-        <v>1090</v>
+      <c r="F9" s="5">
+        <f t="shared" si="0"/>
+        <v>1190</v>
       </c>
       <c r="G9" s="11">
         <v>1500</v>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="F10" s="5">
         <f t="shared" si="0"/>
-        <v>1190</v>
+        <v>1290</v>
       </c>
       <c r="G10" s="5">
         <v>1900</v>
@@ -8743,9 +8743,9 @@
       <c r="E11" s="11">
         <v>890</v>
       </c>
-      <c r="F11" s="11">
-        <f t="shared" si="0"/>
-        <v>990</v>
+      <c r="F11" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G11" s="11">
         <v>1900</v>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="F12" s="5">
         <f t="shared" si="0"/>
-        <v>1290</v>
+        <v>1390</v>
       </c>
       <c r="G12" s="5">
         <v>2000</v>
@@ -8811,9 +8811,9 @@
       <c r="E13" s="11">
         <v>890</v>
       </c>
-      <c r="F13" s="11">
-        <f t="shared" si="0"/>
-        <v>990</v>
+      <c r="F13" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G13" s="11">
         <v>1430</v>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="F14" s="5">
         <f t="shared" si="0"/>
-        <v>1490</v>
+        <v>1590</v>
       </c>
       <c r="G14" s="5">
         <v>2500</v>
@@ -8877,9 +8877,9 @@
       <c r="E15" s="11">
         <v>1290</v>
       </c>
-      <c r="F15" s="11">
-        <f t="shared" si="0"/>
-        <v>1390</v>
+      <c r="F15" s="5">
+        <f t="shared" si="0"/>
+        <v>1490</v>
       </c>
       <c r="G15" s="11">
         <v>1990</v>
@@ -8911,7 +8911,7 @@
       </c>
       <c r="F16" s="5">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1190</v>
       </c>
       <c r="G16" s="5">
         <v>1990</v>
@@ -8941,9 +8941,9 @@
       <c r="E17" s="11">
         <v>2890</v>
       </c>
-      <c r="F17" s="11">
-        <f t="shared" si="0"/>
-        <v>2990</v>
+      <c r="F17" s="5">
+        <f t="shared" si="0"/>
+        <v>3090</v>
       </c>
       <c r="G17" s="11">
         <v>3950</v>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="F18" s="5">
         <f t="shared" si="0"/>
-        <v>2290</v>
+        <v>2390</v>
       </c>
       <c r="G18" s="5">
         <v>3700</v>
@@ -9005,9 +9005,9 @@
       <c r="E19" s="11">
         <v>2490</v>
       </c>
-      <c r="F19" s="11">
-        <f t="shared" si="0"/>
-        <v>2590</v>
+      <c r="F19" s="5">
+        <f t="shared" si="0"/>
+        <v>2690</v>
       </c>
       <c r="G19" s="11">
         <v>3800</v>
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F20" s="5">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>930</v>
       </c>
       <c r="G20" s="5">
         <v>1390</v>
@@ -9073,9 +9073,9 @@
       <c r="E21" s="11">
         <v>1890</v>
       </c>
-      <c r="F21" s="11">
-        <f t="shared" si="0"/>
-        <v>1990</v>
+      <c r="F21" s="5">
+        <f t="shared" si="0"/>
+        <v>2090</v>
       </c>
       <c r="G21" s="11">
         <v>3220</v>
@@ -9109,7 +9109,7 @@
       </c>
       <c r="F22" s="5">
         <f t="shared" si="0"/>
-        <v>1790</v>
+        <v>1890</v>
       </c>
       <c r="G22" s="5">
         <v>3235</v>
@@ -9141,9 +9141,9 @@
       <c r="E23" s="11">
         <v>1490</v>
       </c>
-      <c r="F23" s="11">
-        <f t="shared" si="0"/>
-        <v>1590</v>
+      <c r="F23" s="5">
+        <f t="shared" si="0"/>
+        <v>1690</v>
       </c>
       <c r="G23" s="11">
         <v>3000</v>
@@ -9177,7 +9177,7 @@
       </c>
       <c r="F24" s="5">
         <f t="shared" si="0"/>
-        <v>1990</v>
+        <v>2090</v>
       </c>
       <c r="G24" s="5">
         <v>3500</v>
@@ -9209,9 +9209,9 @@
       <c r="E25" s="11">
         <v>2190</v>
       </c>
-      <c r="F25" s="11">
-        <f t="shared" si="0"/>
-        <v>2290</v>
+      <c r="F25" s="5">
+        <f t="shared" si="0"/>
+        <v>2390</v>
       </c>
       <c r="G25" s="11">
         <v>3850</v>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="F26" s="5">
         <f t="shared" si="0"/>
-        <v>2550</v>
+        <v>2650</v>
       </c>
       <c r="G26" s="5">
         <v>3150</v>
@@ -9275,9 +9275,9 @@
       <c r="E27" s="11">
         <v>1390</v>
       </c>
-      <c r="F27" s="11">
-        <f t="shared" si="0"/>
-        <v>1490</v>
+      <c r="F27" s="5">
+        <f t="shared" si="0"/>
+        <v>1590</v>
       </c>
       <c r="G27" s="11">
         <v>2900</v>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="F28" s="5">
         <f t="shared" si="0"/>
-        <v>1390</v>
+        <v>1490</v>
       </c>
       <c r="G28" s="5">
         <v>2650</v>
@@ -9341,9 +9341,9 @@
       <c r="E29" s="11">
         <v>2190</v>
       </c>
-      <c r="F29" s="11">
-        <f t="shared" si="0"/>
-        <v>2290</v>
+      <c r="F29" s="5">
+        <f t="shared" si="0"/>
+        <v>2390</v>
       </c>
       <c r="G29" s="11">
         <v>3850</v>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="F30" s="5">
         <f t="shared" si="0"/>
-        <v>2990</v>
+        <v>3090</v>
       </c>
       <c r="G30" s="5">
         <v>3800</v>
@@ -9409,9 +9409,9 @@
       <c r="E31" s="11">
         <v>2390</v>
       </c>
-      <c r="F31" s="11">
-        <f t="shared" si="0"/>
-        <v>2490</v>
+      <c r="F31" s="5">
+        <f t="shared" si="0"/>
+        <v>2590</v>
       </c>
       <c r="G31" s="11">
         <v>3700</v>
@@ -9443,7 +9443,7 @@
       </c>
       <c r="F32" s="5">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1190</v>
       </c>
       <c r="G32" s="5">
         <v>2400</v>
@@ -9473,9 +9473,9 @@
       <c r="E33" s="11">
         <v>1390</v>
       </c>
-      <c r="F33" s="11">
-        <f t="shared" si="0"/>
-        <v>1490</v>
+      <c r="F33" s="5">
+        <f t="shared" si="0"/>
+        <v>1590</v>
       </c>
       <c r="G33" s="11">
         <v>1590</v>
@@ -9506,8 +9506,8 @@
         <v>1590</v>
       </c>
       <c r="F34" s="5">
-        <f t="shared" ref="F34:F65" si="1">E34+100</f>
-        <v>1690</v>
+        <f t="shared" si="0"/>
+        <v>1790</v>
       </c>
       <c r="G34" s="5">
         <v>3550</v>
@@ -9537,9 +9537,9 @@
       <c r="E35" s="11">
         <v>1890</v>
       </c>
-      <c r="F35" s="11">
-        <f t="shared" si="1"/>
-        <v>1990</v>
+      <c r="F35" s="5">
+        <f t="shared" si="0"/>
+        <v>2090</v>
       </c>
       <c r="G35" s="11">
         <v>3850</v>
@@ -9572,8 +9572,8 @@
         <v>1290</v>
       </c>
       <c r="F36" s="5">
-        <f t="shared" si="1"/>
-        <v>1390</v>
+        <f t="shared" si="0"/>
+        <v>1490</v>
       </c>
       <c r="G36" s="5">
         <v>3650</v>
@@ -9605,9 +9605,9 @@
       <c r="E37" s="11">
         <v>1590</v>
       </c>
-      <c r="F37" s="11">
-        <f t="shared" si="1"/>
-        <v>1690</v>
+      <c r="F37" s="5">
+        <f t="shared" si="0"/>
+        <v>1790</v>
       </c>
       <c r="G37" s="11">
         <v>2950</v>
@@ -9638,8 +9638,8 @@
         <v>1790</v>
       </c>
       <c r="F38" s="5">
-        <f t="shared" si="1"/>
-        <v>1890</v>
+        <f t="shared" si="0"/>
+        <v>1990</v>
       </c>
       <c r="G38" s="5">
         <v>3400</v>
@@ -9669,9 +9669,9 @@
       <c r="E39" s="11">
         <v>1390</v>
       </c>
-      <c r="F39" s="11">
-        <f t="shared" si="1"/>
-        <v>1490</v>
+      <c r="F39" s="5">
+        <f t="shared" si="0"/>
+        <v>1590</v>
       </c>
       <c r="G39" s="11">
         <v>3150</v>
@@ -9702,8 +9702,8 @@
         <v>1090</v>
       </c>
       <c r="F40" s="5">
-        <f t="shared" si="1"/>
-        <v>1190</v>
+        <f t="shared" si="0"/>
+        <v>1290</v>
       </c>
       <c r="G40" s="5">
         <v>1700</v>
@@ -9735,9 +9735,9 @@
       <c r="E41" s="11">
         <v>1090</v>
       </c>
-      <c r="F41" s="11">
-        <f t="shared" si="1"/>
-        <v>1190</v>
+      <c r="F41" s="5">
+        <f t="shared" si="0"/>
+        <v>1290</v>
       </c>
       <c r="G41" s="11">
         <v>1500</v>
@@ -9770,8 +9770,8 @@
         <v>1990</v>
       </c>
       <c r="F42" s="5">
-        <f t="shared" si="1"/>
-        <v>2090</v>
+        <f t="shared" si="0"/>
+        <v>2190</v>
       </c>
       <c r="G42" s="5">
         <v>3800</v>
@@ -9801,9 +9801,9 @@
       <c r="E43" s="11">
         <v>890</v>
       </c>
-      <c r="F43" s="11">
-        <f t="shared" si="1"/>
-        <v>990</v>
+      <c r="F43" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G43" s="11">
         <v>1700</v>
@@ -9836,8 +9836,8 @@
         <v>1290</v>
       </c>
       <c r="F44" s="5">
-        <f t="shared" si="1"/>
-        <v>1390</v>
+        <f t="shared" si="0"/>
+        <v>1490</v>
       </c>
       <c r="G44" s="5">
         <v>1700</v>
@@ -9867,9 +9867,9 @@
       <c r="E45" s="11">
         <v>750</v>
       </c>
-      <c r="F45" s="11">
-        <f t="shared" si="1"/>
-        <v>850</v>
+      <c r="F45" s="5">
+        <f t="shared" si="0"/>
+        <v>950</v>
       </c>
       <c r="G45" s="11">
         <v>1700</v>
@@ -9902,8 +9902,8 @@
         <v>890</v>
       </c>
       <c r="F46" s="5">
-        <f t="shared" si="1"/>
-        <v>990</v>
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G46" s="5">
         <v>2100</v>
@@ -9935,9 +9935,9 @@
       <c r="E47" s="11">
         <v>1690</v>
       </c>
-      <c r="F47" s="11">
-        <f t="shared" si="1"/>
-        <v>1790</v>
+      <c r="F47" s="5">
+        <f t="shared" si="0"/>
+        <v>1890</v>
       </c>
       <c r="G47" s="11">
         <v>2700</v>
@@ -9970,8 +9970,8 @@
         <v>1690</v>
       </c>
       <c r="F48" s="5">
-        <f t="shared" si="1"/>
-        <v>1790</v>
+        <f t="shared" si="0"/>
+        <v>1890</v>
       </c>
       <c r="G48" s="5">
         <v>2500</v>
@@ -10003,9 +10003,9 @@
       <c r="E49" s="11">
         <v>1990</v>
       </c>
-      <c r="F49" s="11">
-        <f t="shared" si="1"/>
-        <v>2090</v>
+      <c r="F49" s="5">
+        <f t="shared" si="0"/>
+        <v>2190</v>
       </c>
       <c r="G49" s="11">
         <v>3600</v>
@@ -10038,8 +10038,8 @@
         <v>1990</v>
       </c>
       <c r="F50" s="5">
-        <f t="shared" si="1"/>
-        <v>2090</v>
+        <f t="shared" si="0"/>
+        <v>2190</v>
       </c>
       <c r="G50" s="5">
         <v>3650</v>
@@ -10069,9 +10069,9 @@
       <c r="E51" s="11">
         <v>790</v>
       </c>
-      <c r="F51" s="11">
-        <f t="shared" si="1"/>
-        <v>890</v>
+      <c r="F51" s="5">
+        <f t="shared" si="0"/>
+        <v>990</v>
       </c>
       <c r="G51" s="11">
         <v>1300</v>
@@ -10104,8 +10104,8 @@
         <v>990</v>
       </c>
       <c r="F52" s="5">
-        <f t="shared" si="1"/>
-        <v>1090</v>
+        <f t="shared" si="0"/>
+        <v>1190</v>
       </c>
       <c r="G52" s="5">
         <v>1390</v>
@@ -10137,9 +10137,9 @@
       <c r="E53" s="11">
         <v>640</v>
       </c>
-      <c r="F53" s="11">
-        <f t="shared" si="1"/>
-        <v>740</v>
+      <c r="F53" s="5">
+        <f t="shared" si="0"/>
+        <v>840</v>
       </c>
       <c r="G53" s="11">
         <v>900</v>
@@ -10172,8 +10172,8 @@
         <v>890</v>
       </c>
       <c r="F54" s="5">
-        <f t="shared" si="1"/>
-        <v>990</v>
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G54" s="5">
         <v>1300</v>
@@ -10205,9 +10205,9 @@
       <c r="E55" s="11">
         <v>690</v>
       </c>
-      <c r="F55" s="11">
-        <f t="shared" si="1"/>
-        <v>790</v>
+      <c r="F55" s="5">
+        <f t="shared" si="0"/>
+        <v>890</v>
       </c>
       <c r="G55" s="11">
         <v>800</v>
@@ -10240,8 +10240,8 @@
         <v>930</v>
       </c>
       <c r="F56" s="5">
-        <f t="shared" si="1"/>
-        <v>1030</v>
+        <f t="shared" si="0"/>
+        <v>1130</v>
       </c>
       <c r="G56" s="5">
         <v>1200</v>
@@ -10275,9 +10275,9 @@
       <c r="E57" s="11">
         <v>890</v>
       </c>
-      <c r="F57" s="11">
-        <f t="shared" si="1"/>
-        <v>990</v>
+      <c r="F57" s="5">
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G57" s="11">
         <v>1400</v>
@@ -10310,8 +10310,8 @@
         <v>890</v>
       </c>
       <c r="F58" s="5">
-        <f t="shared" si="1"/>
-        <v>990</v>
+        <f t="shared" si="0"/>
+        <v>1090</v>
       </c>
       <c r="G58" s="5">
         <v>1120</v>
@@ -10343,9 +10343,9 @@
       <c r="E59" s="11">
         <v>1090</v>
       </c>
-      <c r="F59" s="11">
-        <f t="shared" si="1"/>
-        <v>1190</v>
+      <c r="F59" s="5">
+        <f t="shared" si="0"/>
+        <v>1290</v>
       </c>
       <c r="G59" s="11">
         <v>1300</v>
@@ -10378,8 +10378,8 @@
         <v>690</v>
       </c>
       <c r="F60" s="5">
-        <f t="shared" si="1"/>
-        <v>790</v>
+        <f t="shared" si="0"/>
+        <v>890</v>
       </c>
       <c r="G60" s="5">
         <v>1000</v>
@@ -10411,9 +10411,9 @@
       <c r="E61" s="11">
         <v>790</v>
       </c>
-      <c r="F61" s="11">
-        <f t="shared" si="1"/>
-        <v>890</v>
+      <c r="F61" s="5">
+        <f t="shared" si="0"/>
+        <v>990</v>
       </c>
       <c r="G61" s="11">
         <v>1400</v>
@@ -10446,8 +10446,8 @@
         <v>690</v>
       </c>
       <c r="F62" s="5">
-        <f t="shared" si="1"/>
-        <v>790</v>
+        <f t="shared" si="0"/>
+        <v>890</v>
       </c>
       <c r="G62" s="5">
         <v>1200</v>
@@ -10477,9 +10477,9 @@
       <c r="E63" s="11">
         <v>690</v>
       </c>
-      <c r="F63" s="11">
-        <f t="shared" si="1"/>
-        <v>790</v>
+      <c r="F63" s="5">
+        <f t="shared" si="0"/>
+        <v>890</v>
       </c>
       <c r="G63" s="11">
         <v>1000</v>
@@ -10510,8 +10510,8 @@
         <v>1790</v>
       </c>
       <c r="F64" s="5">
-        <f t="shared" si="1"/>
-        <v>1890</v>
+        <f t="shared" si="0"/>
+        <v>1990</v>
       </c>
       <c r="G64" s="5">
         <v>3000</v>
@@ -10541,9 +10541,9 @@
       <c r="E65" s="11">
         <v>1890</v>
       </c>
-      <c r="F65" s="11">
-        <f t="shared" si="1"/>
-        <v>1990</v>
+      <c r="F65" s="5">
+        <f t="shared" si="0"/>
+        <v>2090</v>
       </c>
       <c r="G65" s="11">
         <v>3650</v>
@@ -10574,8 +10574,8 @@
         <v>990</v>
       </c>
       <c r="F66" s="5">
-        <f t="shared" ref="F66:F85" si="2">E66+100</f>
-        <v>1090</v>
+        <f t="shared" si="0"/>
+        <v>1190</v>
       </c>
       <c r="G66" s="5">
         <v>2690</v>
@@ -10607,9 +10607,9 @@
       <c r="E67" s="11">
         <v>1190</v>
       </c>
-      <c r="F67" s="11">
-        <f t="shared" si="2"/>
-        <v>1290</v>
+      <c r="F67" s="5">
+        <f t="shared" ref="F67:F85" si="1">E67+200</f>
+        <v>1390</v>
       </c>
       <c r="G67" s="11">
         <v>2600</v>
@@ -10642,8 +10642,8 @@
         <v>890</v>
       </c>
       <c r="F68" s="5">
-        <f t="shared" si="2"/>
-        <v>990</v>
+        <f t="shared" si="1"/>
+        <v>1090</v>
       </c>
       <c r="G68" s="5">
         <v>1300</v>
@@ -10675,9 +10675,9 @@
       <c r="E69" s="11">
         <v>1190</v>
       </c>
-      <c r="F69" s="11">
-        <f t="shared" si="2"/>
-        <v>1290</v>
+      <c r="F69" s="5">
+        <f t="shared" si="1"/>
+        <v>1390</v>
       </c>
       <c r="G69" s="11">
         <v>3100</v>
@@ -10710,8 +10710,8 @@
         <v>1290</v>
       </c>
       <c r="F70" s="5">
-        <f t="shared" si="2"/>
-        <v>1390</v>
+        <f t="shared" si="1"/>
+        <v>1490</v>
       </c>
       <c r="G70" s="5">
         <v>1800</v>
@@ -10743,9 +10743,9 @@
       <c r="E71" s="11">
         <v>1190</v>
       </c>
-      <c r="F71" s="11">
-        <f t="shared" si="2"/>
-        <v>1290</v>
+      <c r="F71" s="5">
+        <f t="shared" si="1"/>
+        <v>1390</v>
       </c>
       <c r="G71" s="11">
         <v>3100</v>
@@ -10778,8 +10778,8 @@
         <v>1490</v>
       </c>
       <c r="F72" s="5">
-        <f t="shared" si="2"/>
-        <v>1590</v>
+        <f t="shared" si="1"/>
+        <v>1690</v>
       </c>
       <c r="G72" s="5">
         <v>3390</v>
@@ -10809,9 +10809,9 @@
       <c r="E73" s="11">
         <v>2490</v>
       </c>
-      <c r="F73" s="11">
-        <f t="shared" si="2"/>
-        <v>2590</v>
+      <c r="F73" s="5">
+        <f t="shared" si="1"/>
+        <v>2690</v>
       </c>
       <c r="G73" s="11">
         <v>3800</v>
@@ -10844,8 +10844,8 @@
         <v>1190</v>
       </c>
       <c r="F74" s="5">
-        <f t="shared" si="2"/>
-        <v>1290</v>
+        <f t="shared" si="1"/>
+        <v>1390</v>
       </c>
       <c r="G74" s="5">
         <v>1990</v>
@@ -10877,9 +10877,9 @@
       <c r="E75" s="11">
         <v>1190</v>
       </c>
-      <c r="F75" s="11">
-        <f t="shared" si="2"/>
-        <v>1290</v>
+      <c r="F75" s="5">
+        <f t="shared" si="1"/>
+        <v>1390</v>
       </c>
       <c r="G75" s="11">
         <v>1800</v>
@@ -10910,8 +10910,8 @@
         <v>2590</v>
       </c>
       <c r="F76" s="5">
-        <f t="shared" si="2"/>
-        <v>2690</v>
+        <f t="shared" si="1"/>
+        <v>2790</v>
       </c>
       <c r="G76" s="5">
         <v>3800</v>
@@ -10943,9 +10943,9 @@
       <c r="E77" s="11">
         <v>2590</v>
       </c>
-      <c r="F77" s="11">
-        <f t="shared" si="2"/>
-        <v>2690</v>
+      <c r="F77" s="5">
+        <f t="shared" si="1"/>
+        <v>2790</v>
       </c>
       <c r="G77" s="11">
         <v>3800</v>
@@ -10978,8 +10978,8 @@
         <v>2890</v>
       </c>
       <c r="F78" s="5">
-        <f t="shared" si="2"/>
-        <v>2990</v>
+        <f t="shared" si="1"/>
+        <v>3090</v>
       </c>
       <c r="G78" s="5">
         <v>3940</v>
@@ -11009,9 +11009,9 @@
       <c r="E79" s="11">
         <v>890</v>
       </c>
-      <c r="F79" s="11">
-        <f t="shared" si="2"/>
-        <v>990</v>
+      <c r="F79" s="5">
+        <f t="shared" si="1"/>
+        <v>1090</v>
       </c>
       <c r="G79" s="11">
         <v>1700</v>
@@ -11044,8 +11044,8 @@
         <v>1390</v>
       </c>
       <c r="F80" s="5">
-        <f t="shared" si="2"/>
-        <v>1490</v>
+        <f t="shared" si="1"/>
+        <v>1590</v>
       </c>
       <c r="G80" s="5">
         <v>2900</v>
@@ -11077,9 +11077,9 @@
       <c r="E81" s="11">
         <v>1490</v>
       </c>
-      <c r="F81" s="11">
-        <f t="shared" si="2"/>
-        <v>1590</v>
+      <c r="F81" s="5">
+        <f t="shared" si="1"/>
+        <v>1690</v>
       </c>
       <c r="G81" s="11">
         <v>3300</v>
@@ -11112,8 +11112,8 @@
         <v>1390</v>
       </c>
       <c r="F82" s="5">
-        <f t="shared" si="2"/>
-        <v>1490</v>
+        <f t="shared" si="1"/>
+        <v>1590</v>
       </c>
       <c r="G82" s="5">
         <v>2900</v>
@@ -11143,9 +11143,9 @@
       <c r="E83" s="11">
         <v>2350</v>
       </c>
-      <c r="F83" s="11">
-        <f t="shared" si="2"/>
-        <v>2450</v>
+      <c r="F83" s="5">
+        <f t="shared" si="1"/>
+        <v>2550</v>
       </c>
       <c r="G83" s="11">
         <v>3800</v>
@@ -11176,8 +11176,8 @@
         <v>2450</v>
       </c>
       <c r="F84" s="5">
-        <f t="shared" si="2"/>
-        <v>2550</v>
+        <f t="shared" si="1"/>
+        <v>2650</v>
       </c>
       <c r="G84" s="5">
         <v>3800</v>
@@ -11207,9 +11207,9 @@
       <c r="E85" s="11">
         <v>2590</v>
       </c>
-      <c r="F85" s="11">
-        <f t="shared" si="2"/>
-        <v>2690</v>
+      <c r="F85" s="5">
+        <f t="shared" si="1"/>
+        <v>2790</v>
       </c>
       <c r="G85" s="11">
         <v>3940</v>
